--- a/data/histories/La Primera History.xlsx
+++ b/data/histories/La Primera History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2753"/>
+  <dimension ref="A1:E2756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74759,6 +74759,87 @@
         </is>
       </c>
     </row>
+    <row r="2754">
+      <c r="A2754" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2754" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2754" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D2754" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E2754" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="2755">
+      <c r="A2755" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B2755" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera</t>
+        </is>
+      </c>
+      <c r="C2755" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D2755" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E2755" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="2756">
+      <c r="A2756" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B2756" t="inlineStr">
+        <is>
+          <t>Quiniela La Primera Noche</t>
+        </is>
+      </c>
+      <c r="C2756" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D2756" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E2756" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
